--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.4815629520662</v>
+        <v>8.690753979710758</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60041566553099</v>
+        <v>2.697567545648786</v>
       </c>
       <c r="E2" t="n">
-        <v>7.985768515017206</v>
+        <v>1.297687383690296</v>
       </c>
       <c r="F2" t="n">
-        <v>15.586334732612</v>
+        <v>2.532779394049451</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.40853474021832</v>
+        <v>9.166386895285477</v>
       </c>
       <c r="D3" t="n">
-        <v>54.70790393215005</v>
+        <v>8.890034388974383</v>
       </c>
       <c r="E3" t="n">
-        <v>7.985768515017206</v>
+        <v>1.297687383690296</v>
       </c>
       <c r="F3" t="n">
-        <v>15.586334732612</v>
+        <v>2.532779394049451</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.19539596606735</v>
+        <v>6.206751844485945</v>
       </c>
       <c r="D4" t="n">
-        <v>37.67077584899502</v>
+        <v>6.121501075461691</v>
       </c>
       <c r="E4" t="n">
-        <v>7.985768515017206</v>
+        <v>1.297687383690296</v>
       </c>
       <c r="F4" t="n">
-        <v>15.586334732612</v>
+        <v>2.532779394049451</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
